--- a/forms/trg/Formulir_TRG_algebra.xlsx
+++ b/forms/trg/Formulir_TRG_algebra.xlsx
@@ -928,7 +928,11 @@
           <t>Dra. Nur Erawaty, M.Si</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
